--- a/research/traditional_assets/database/data/norway/norway_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.168</v>
+        <v>-0.121</v>
       </c>
       <c r="E2">
-        <v>0.0827</v>
+        <v>0.00123</v>
       </c>
       <c r="F2">
-        <v>0.08650000000000001</v>
+        <v>0.0621</v>
       </c>
       <c r="G2">
-        <v>0.03048972894512638</v>
+        <v>0.2476028765481422</v>
       </c>
       <c r="H2">
-        <v>0.03048972894512638</v>
+        <v>0.2476028765481422</v>
       </c>
       <c r="I2">
-        <v>0.03732132151083904</v>
+        <v>0.1443268078306033</v>
       </c>
       <c r="J2">
-        <v>0.02991629740154558</v>
+        <v>0.1409156607832622</v>
       </c>
       <c r="K2">
-        <v>353.6</v>
+        <v>239.6</v>
       </c>
       <c r="L2">
-        <v>0.02789435486415702</v>
+        <v>0.1196564123052337</v>
       </c>
       <c r="M2">
-        <v>190.8</v>
+        <v>189.7</v>
       </c>
       <c r="N2">
-        <v>0.04039035542666018</v>
+        <v>0.04714331867094113</v>
       </c>
       <c r="O2">
-        <v>0.5395927601809954</v>
+        <v>0.7917362270450751</v>
       </c>
       <c r="P2">
-        <v>174.3</v>
+        <v>152.6</v>
       </c>
       <c r="Q2">
-        <v>0.03689747877812825</v>
+        <v>0.03792340763935485</v>
       </c>
       <c r="R2">
-        <v>0.4929298642533937</v>
+        <v>0.6368948247078464</v>
       </c>
       <c r="S2">
-        <v>16.5</v>
+        <v>37.09999999999999</v>
       </c>
       <c r="T2">
-        <v>0.08647798742138364</v>
+        <v>0.1955719557195572</v>
       </c>
       <c r="U2">
-        <v>518.2</v>
+        <v>440.9</v>
       </c>
       <c r="V2">
-        <v>0.1096974957132878</v>
+        <v>0.109570317353811</v>
       </c>
       <c r="W2">
-        <v>0.09413017436443498</v>
+        <v>0.05690670720121604</v>
       </c>
       <c r="X2">
-        <v>0.08492007397052745</v>
+        <v>0.1239794732421076</v>
       </c>
       <c r="Y2">
-        <v>0.00921010039390753</v>
+        <v>-0.06707276604089155</v>
       </c>
       <c r="Z2">
-        <v>1.848356711673617</v>
+        <v>0.2430923129218667</v>
       </c>
       <c r="AA2">
-        <v>0.05529598909057077</v>
+        <v>0.03425551390671639</v>
       </c>
       <c r="AB2">
-        <v>0.05514028862728405</v>
+        <v>0.0838142350699181</v>
       </c>
       <c r="AC2">
-        <v>0.0001557004632867162</v>
+        <v>-0.04955872116320171</v>
       </c>
       <c r="AD2">
-        <v>4545</v>
+        <v>4098.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4545</v>
+        <v>4098.7</v>
       </c>
       <c r="AG2">
-        <v>4026.8</v>
+        <v>3657.8</v>
       </c>
       <c r="AH2">
-        <v>0.4903494481545815</v>
+        <v>0.50460443700293</v>
       </c>
       <c r="AI2">
-        <v>0.5191082075062248</v>
+        <v>0.5436085837820632</v>
       </c>
       <c r="AJ2">
-        <v>0.4601689007736524</v>
+        <v>0.4761706393116107</v>
       </c>
       <c r="AK2">
-        <v>0.4888554363133104</v>
+        <v>0.5152629280592768</v>
       </c>
       <c r="AL2">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="AM2">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="AN2">
-        <v>9.245321399511798</v>
+        <v>13.20883016435707</v>
       </c>
       <c r="AO2">
-        <v>5.142391304347826</v>
+        <v>3.016701461377871</v>
       </c>
       <c r="AP2">
-        <v>8.191212367778682</v>
+        <v>11.78794714792136</v>
       </c>
       <c r="AQ2">
-        <v>5.142391304347826</v>
+        <v>3.016701461377871</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.168</v>
+        <v>-0.121</v>
       </c>
       <c r="E3">
-        <v>0.0827</v>
+        <v>0.00123</v>
       </c>
       <c r="F3">
-        <v>0.08650000000000001</v>
+        <v>0.0621</v>
       </c>
       <c r="G3">
-        <v>0.03048972894512638</v>
+        <v>0.2476028765481422</v>
       </c>
       <c r="H3">
-        <v>0.03048972894512638</v>
+        <v>0.2476028765481422</v>
       </c>
       <c r="I3">
-        <v>0.03732132151083904</v>
+        <v>0.1443268078306033</v>
       </c>
       <c r="J3">
-        <v>0.02991629740154558</v>
+        <v>0.1409156607832622</v>
       </c>
       <c r="K3">
-        <v>353.6</v>
+        <v>239.6</v>
       </c>
       <c r="L3">
-        <v>0.02789435486415702</v>
+        <v>0.1196564123052337</v>
       </c>
       <c r="M3">
-        <v>190.8</v>
+        <v>189.7</v>
       </c>
       <c r="N3">
-        <v>0.04039035542666018</v>
+        <v>0.04714331867094113</v>
       </c>
       <c r="O3">
-        <v>0.5395927601809954</v>
+        <v>0.7917362270450751</v>
       </c>
       <c r="P3">
-        <v>174.3</v>
+        <v>152.6</v>
       </c>
       <c r="Q3">
-        <v>0.03689747877812825</v>
+        <v>0.03792340763935485</v>
       </c>
       <c r="R3">
-        <v>0.4929298642533937</v>
+        <v>0.6368948247078464</v>
       </c>
       <c r="S3">
-        <v>16.5</v>
+        <v>37.09999999999999</v>
       </c>
       <c r="T3">
-        <v>0.08647798742138364</v>
+        <v>0.1955719557195572</v>
       </c>
       <c r="U3">
-        <v>518.2</v>
+        <v>440.9</v>
       </c>
       <c r="V3">
-        <v>0.1096974957132878</v>
+        <v>0.109570317353811</v>
       </c>
       <c r="W3">
-        <v>0.09413017436443498</v>
+        <v>0.05690670720121604</v>
       </c>
       <c r="X3">
-        <v>0.08492007397052745</v>
+        <v>0.1239794732421076</v>
       </c>
       <c r="Y3">
-        <v>0.00921010039390753</v>
+        <v>-0.06707276604089155</v>
       </c>
       <c r="Z3">
-        <v>1.848356711673617</v>
+        <v>0.2430923129218667</v>
       </c>
       <c r="AA3">
-        <v>0.05529598909057077</v>
+        <v>0.03425551390671639</v>
       </c>
       <c r="AB3">
-        <v>0.05514028862728405</v>
+        <v>0.0838142350699181</v>
       </c>
       <c r="AC3">
-        <v>0.0001557004632867162</v>
+        <v>-0.04955872116320171</v>
       </c>
       <c r="AD3">
-        <v>4545</v>
+        <v>4098.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4545</v>
+        <v>4098.7</v>
       </c>
       <c r="AG3">
-        <v>4026.8</v>
+        <v>3657.8</v>
       </c>
       <c r="AH3">
-        <v>0.4903494481545815</v>
+        <v>0.50460443700293</v>
       </c>
       <c r="AI3">
-        <v>0.5191082075062248</v>
+        <v>0.5436085837820632</v>
       </c>
       <c r="AJ3">
-        <v>0.4601689007736524</v>
+        <v>0.4761706393116107</v>
       </c>
       <c r="AK3">
-        <v>0.4888554363133104</v>
+        <v>0.5152629280592768</v>
       </c>
       <c r="AL3">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="AM3">
-        <v>92</v>
+        <v>95.8</v>
       </c>
       <c r="AN3">
-        <v>9.245321399511798</v>
+        <v>13.20883016435707</v>
       </c>
       <c r="AO3">
-        <v>5.142391304347826</v>
+        <v>3.016701461377871</v>
       </c>
       <c r="AP3">
-        <v>8.191212367778682</v>
+        <v>11.78794714792136</v>
       </c>
       <c r="AQ3">
-        <v>5.142391304347826</v>
+        <v>3.016701461377871</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.121</v>
+        <v>0.187</v>
       </c>
       <c r="E2">
-        <v>0.00123</v>
+        <v>0.049</v>
       </c>
       <c r="F2">
-        <v>0.0621</v>
+        <v>0.141</v>
       </c>
       <c r="G2">
-        <v>0.2476028765481422</v>
+        <v>0.03766354157707121</v>
       </c>
       <c r="H2">
-        <v>0.2476028765481422</v>
+        <v>0.03766354157707121</v>
       </c>
       <c r="I2">
-        <v>0.1443268078306033</v>
+        <v>0.8700746389900322</v>
       </c>
       <c r="J2">
-        <v>0.1409156607832622</v>
+        <v>0.8700746389900322</v>
       </c>
       <c r="K2">
-        <v>239.6</v>
+        <v>275.5</v>
       </c>
       <c r="L2">
-        <v>0.1196564123052337</v>
+        <v>0.02632911876296147</v>
       </c>
       <c r="M2">
-        <v>189.7</v>
+        <v>279.3</v>
       </c>
       <c r="N2">
-        <v>0.04714331867094113</v>
+        <v>0.07032076136764187</v>
       </c>
       <c r="O2">
-        <v>0.7917362270450751</v>
+        <v>1.013793103448276</v>
       </c>
       <c r="P2">
-        <v>152.6</v>
+        <v>163</v>
       </c>
       <c r="Q2">
-        <v>0.03792340763935485</v>
+        <v>0.041039327257163</v>
       </c>
       <c r="R2">
-        <v>0.6368948247078464</v>
+        <v>0.5916515426497277</v>
       </c>
       <c r="S2">
-        <v>37.09999999999999</v>
+        <v>116.3</v>
       </c>
       <c r="T2">
-        <v>0.1955719557195572</v>
+        <v>0.4163981382026495</v>
       </c>
       <c r="U2">
-        <v>440.9</v>
+        <v>1487.7</v>
       </c>
       <c r="V2">
-        <v>0.109570317353811</v>
+        <v>0.3745656881011128</v>
       </c>
       <c r="W2">
-        <v>0.05690670720121604</v>
+        <v>0.0800616082066781</v>
       </c>
       <c r="X2">
-        <v>0.1239794732421076</v>
+        <v>0.1075088799082786</v>
       </c>
       <c r="Y2">
-        <v>-0.06707276604089155</v>
+        <v>-0.02744727170160054</v>
       </c>
       <c r="Z2">
-        <v>0.2430923129218667</v>
+        <v>1.473988927862063</v>
       </c>
       <c r="AA2">
-        <v>0.03425551390671639</v>
+        <v>1.282480384284889</v>
       </c>
       <c r="AB2">
-        <v>0.0838142350699181</v>
+        <v>0.07137906968830357</v>
       </c>
       <c r="AC2">
-        <v>-0.04955872116320171</v>
+        <v>1.211101314596586</v>
       </c>
       <c r="AD2">
-        <v>4098.7</v>
+        <v>4678.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4098.7</v>
+        <v>4678.6</v>
       </c>
       <c r="AG2">
-        <v>3657.8</v>
+        <v>3190.900000000001</v>
       </c>
       <c r="AH2">
-        <v>0.50460443700293</v>
+        <v>0.5408536021455654</v>
       </c>
       <c r="AI2">
-        <v>0.5436085837820632</v>
+        <v>0.6329018032276829</v>
       </c>
       <c r="AJ2">
-        <v>0.4761706393116107</v>
+        <v>0.4454884331327572</v>
       </c>
       <c r="AK2">
-        <v>0.5152629280592768</v>
+        <v>0.5404091725095689</v>
       </c>
       <c r="AL2">
-        <v>95.8</v>
+        <v>258.4</v>
       </c>
       <c r="AM2">
-        <v>95.8</v>
+        <v>258.4</v>
       </c>
       <c r="AN2">
-        <v>13.20883016435707</v>
+        <v>0.5117250732817081</v>
       </c>
       <c r="AO2">
-        <v>3.016701461377871</v>
+        <v>35.23297213622292</v>
       </c>
       <c r="AP2">
-        <v>11.78794714792136</v>
+        <v>0.34900686879293</v>
       </c>
       <c r="AQ2">
-        <v>3.016701461377871</v>
+        <v>35.23297213622292</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.121</v>
+        <v>0.187</v>
       </c>
       <c r="E3">
-        <v>0.00123</v>
+        <v>0.049</v>
       </c>
       <c r="F3">
-        <v>0.0621</v>
+        <v>0.141</v>
       </c>
       <c r="G3">
-        <v>0.2476028765481422</v>
+        <v>0.03766354157707121</v>
       </c>
       <c r="H3">
-        <v>0.2476028765481422</v>
+        <v>0.03766354157707121</v>
       </c>
       <c r="I3">
-        <v>0.1443268078306033</v>
+        <v>0.8700746389900322</v>
       </c>
       <c r="J3">
-        <v>0.1409156607832622</v>
+        <v>0.8700746389900322</v>
       </c>
       <c r="K3">
-        <v>239.6</v>
+        <v>275.5</v>
       </c>
       <c r="L3">
-        <v>0.1196564123052337</v>
+        <v>0.02632911876296147</v>
       </c>
       <c r="M3">
-        <v>189.7</v>
+        <v>279.3</v>
       </c>
       <c r="N3">
-        <v>0.04714331867094113</v>
+        <v>0.07032076136764187</v>
       </c>
       <c r="O3">
-        <v>0.7917362270450751</v>
+        <v>1.013793103448276</v>
       </c>
       <c r="P3">
-        <v>152.6</v>
+        <v>163</v>
       </c>
       <c r="Q3">
-        <v>0.03792340763935485</v>
+        <v>0.041039327257163</v>
       </c>
       <c r="R3">
-        <v>0.6368948247078464</v>
+        <v>0.5916515426497277</v>
       </c>
       <c r="S3">
-        <v>37.09999999999999</v>
+        <v>116.3</v>
       </c>
       <c r="T3">
-        <v>0.1955719557195572</v>
+        <v>0.4163981382026495</v>
       </c>
       <c r="U3">
-        <v>440.9</v>
+        <v>1487.7</v>
       </c>
       <c r="V3">
-        <v>0.109570317353811</v>
+        <v>0.3745656881011128</v>
       </c>
       <c r="W3">
-        <v>0.05690670720121604</v>
+        <v>0.0800616082066781</v>
       </c>
       <c r="X3">
-        <v>0.1239794732421076</v>
+        <v>0.1075088799082786</v>
       </c>
       <c r="Y3">
-        <v>-0.06707276604089155</v>
+        <v>-0.02744727170160054</v>
       </c>
       <c r="Z3">
-        <v>0.2430923129218667</v>
+        <v>1.473988927862063</v>
       </c>
       <c r="AA3">
-        <v>0.03425551390671639</v>
+        <v>1.282480384284889</v>
       </c>
       <c r="AB3">
-        <v>0.0838142350699181</v>
+        <v>0.07137906968830357</v>
       </c>
       <c r="AC3">
-        <v>-0.04955872116320171</v>
+        <v>1.211101314596586</v>
       </c>
       <c r="AD3">
-        <v>4098.7</v>
+        <v>4678.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4098.7</v>
+        <v>4678.6</v>
       </c>
       <c r="AG3">
-        <v>3657.8</v>
+        <v>3190.900000000001</v>
       </c>
       <c r="AH3">
-        <v>0.50460443700293</v>
+        <v>0.5408536021455654</v>
       </c>
       <c r="AI3">
-        <v>0.5436085837820632</v>
+        <v>0.6329018032276829</v>
       </c>
       <c r="AJ3">
-        <v>0.4761706393116107</v>
+        <v>0.4454884331327572</v>
       </c>
       <c r="AK3">
-        <v>0.5152629280592768</v>
+        <v>0.5404091725095689</v>
       </c>
       <c r="AL3">
-        <v>95.8</v>
+        <v>258.4</v>
       </c>
       <c r="AM3">
-        <v>95.8</v>
+        <v>258.4</v>
       </c>
       <c r="AN3">
-        <v>13.20883016435707</v>
+        <v>0.5117250732817081</v>
       </c>
       <c r="AO3">
-        <v>3.016701461377871</v>
+        <v>35.23297213622292</v>
       </c>
       <c r="AP3">
-        <v>11.78794714792136</v>
+        <v>0.34900686879293</v>
       </c>
       <c r="AQ3">
-        <v>3.016701461377871</v>
+        <v>35.23297213622292</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.187</v>
+        <v>0.08039999999999999</v>
       </c>
       <c r="E2">
-        <v>0.049</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="F2">
-        <v>0.141</v>
+        <v>0.117</v>
       </c>
       <c r="G2">
-        <v>0.03766354157707121</v>
+        <v>0.5338683788121991</v>
       </c>
       <c r="H2">
-        <v>0.03766354157707121</v>
+        <v>0.5338683788121991</v>
       </c>
       <c r="I2">
-        <v>0.8700746389900322</v>
+        <v>0.8444087747458534</v>
       </c>
       <c r="J2">
-        <v>0.8700746389900322</v>
+        <v>0.7510492836335533</v>
       </c>
       <c r="K2">
-        <v>275.5</v>
+        <v>485.9</v>
       </c>
       <c r="L2">
-        <v>0.02632911876296147</v>
+        <v>0.05777302181796563</v>
       </c>
       <c r="M2">
-        <v>279.3</v>
+        <v>346.8</v>
       </c>
       <c r="N2">
-        <v>0.07032076136764187</v>
+        <v>0.07490442558154604</v>
       </c>
       <c r="O2">
-        <v>1.013793103448276</v>
+        <v>0.7137271043424573</v>
       </c>
       <c r="P2">
-        <v>163</v>
+        <v>175.5</v>
       </c>
       <c r="Q2">
-        <v>0.041039327257163</v>
+        <v>0.03790578630207996</v>
       </c>
       <c r="R2">
-        <v>0.5916515426497277</v>
+        <v>0.361185429100638</v>
       </c>
       <c r="S2">
-        <v>116.3</v>
+        <v>171.3</v>
       </c>
       <c r="T2">
-        <v>0.4163981382026495</v>
+        <v>0.4939446366782007</v>
       </c>
       <c r="U2">
-        <v>1487.7</v>
+        <v>1117.3</v>
       </c>
       <c r="V2">
-        <v>0.3745656881011128</v>
+        <v>0.2413227067539256</v>
       </c>
       <c r="W2">
-        <v>0.0800616082066781</v>
+        <v>0.1790544275343627</v>
       </c>
       <c r="X2">
-        <v>0.1075088799082786</v>
+        <v>0.1080474665909721</v>
       </c>
       <c r="Y2">
-        <v>-0.02744727170160054</v>
+        <v>0.07100696094339054</v>
       </c>
       <c r="Z2">
-        <v>1.473988927862063</v>
+        <v>1.424397927039935</v>
       </c>
       <c r="AA2">
-        <v>1.282480384284889</v>
+        <v>1.069793042712461</v>
       </c>
       <c r="AB2">
-        <v>0.07137906968830357</v>
+        <v>0.07472786949627339</v>
       </c>
       <c r="AC2">
-        <v>1.211101314596586</v>
+        <v>0.9950651732161879</v>
       </c>
       <c r="AD2">
-        <v>4678.6</v>
+        <v>5019.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4678.6</v>
+        <v>5019.1</v>
       </c>
       <c r="AG2">
-        <v>3190.900000000001</v>
+        <v>3901.8</v>
       </c>
       <c r="AH2">
-        <v>0.5408536021455654</v>
+        <v>0.5201678930459115</v>
       </c>
       <c r="AI2">
-        <v>0.6329018032276829</v>
+        <v>0.6327739885777682</v>
       </c>
       <c r="AJ2">
-        <v>0.4454884331327572</v>
+        <v>0.4573297232673441</v>
       </c>
       <c r="AK2">
-        <v>0.5404091725095689</v>
+        <v>0.5725647873682975</v>
       </c>
       <c r="AL2">
-        <v>258.4</v>
+        <v>373.6</v>
       </c>
       <c r="AM2">
-        <v>258.4</v>
+        <v>373.6</v>
       </c>
       <c r="AN2">
-        <v>0.5117250732817081</v>
+        <v>0.7040497131394746</v>
       </c>
       <c r="AO2">
-        <v>35.23297213622292</v>
+        <v>19.00936830835117</v>
       </c>
       <c r="AP2">
-        <v>0.34900686879293</v>
+        <v>0.5473214661448471</v>
       </c>
       <c r="AQ2">
-        <v>35.23297213622292</v>
+        <v>19.00936830835117</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.187</v>
+        <v>0.08039999999999999</v>
       </c>
       <c r="E3">
-        <v>0.049</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="F3">
-        <v>0.141</v>
+        <v>0.117</v>
       </c>
       <c r="G3">
-        <v>0.03766354157707121</v>
+        <v>0.5338683788121991</v>
       </c>
       <c r="H3">
-        <v>0.03766354157707121</v>
+        <v>0.5338683788121991</v>
       </c>
       <c r="I3">
-        <v>0.8700746389900322</v>
+        <v>0.8444087747458534</v>
       </c>
       <c r="J3">
-        <v>0.8700746389900322</v>
+        <v>0.7510492836335533</v>
       </c>
       <c r="K3">
-        <v>275.5</v>
+        <v>485.9</v>
       </c>
       <c r="L3">
-        <v>0.02632911876296147</v>
+        <v>0.05777302181796563</v>
       </c>
       <c r="M3">
-        <v>279.3</v>
+        <v>346.8</v>
       </c>
       <c r="N3">
-        <v>0.07032076136764187</v>
+        <v>0.07490442558154604</v>
       </c>
       <c r="O3">
-        <v>1.013793103448276</v>
+        <v>0.7137271043424573</v>
       </c>
       <c r="P3">
-        <v>163</v>
+        <v>175.5</v>
       </c>
       <c r="Q3">
-        <v>0.041039327257163</v>
+        <v>0.03790578630207996</v>
       </c>
       <c r="R3">
-        <v>0.5916515426497277</v>
+        <v>0.361185429100638</v>
       </c>
       <c r="S3">
-        <v>116.3</v>
+        <v>171.3</v>
       </c>
       <c r="T3">
-        <v>0.4163981382026495</v>
+        <v>0.4939446366782007</v>
       </c>
       <c r="U3">
-        <v>1487.7</v>
+        <v>1117.3</v>
       </c>
       <c r="V3">
-        <v>0.3745656881011128</v>
+        <v>0.2413227067539256</v>
       </c>
       <c r="W3">
-        <v>0.0800616082066781</v>
+        <v>0.1790544275343627</v>
       </c>
       <c r="X3">
-        <v>0.1075088799082786</v>
+        <v>0.1080474665909721</v>
       </c>
       <c r="Y3">
-        <v>-0.02744727170160054</v>
+        <v>0.07100696094339054</v>
       </c>
       <c r="Z3">
-        <v>1.473988927862063</v>
+        <v>1.424397927039935</v>
       </c>
       <c r="AA3">
-        <v>1.282480384284889</v>
+        <v>1.069793042712461</v>
       </c>
       <c r="AB3">
-        <v>0.07137906968830357</v>
+        <v>0.07472786949627339</v>
       </c>
       <c r="AC3">
-        <v>1.211101314596586</v>
+        <v>0.9950651732161879</v>
       </c>
       <c r="AD3">
-        <v>4678.6</v>
+        <v>5019.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4678.6</v>
+        <v>5019.1</v>
       </c>
       <c r="AG3">
-        <v>3190.900000000001</v>
+        <v>3901.8</v>
       </c>
       <c r="AH3">
-        <v>0.5408536021455654</v>
+        <v>0.5201678930459115</v>
       </c>
       <c r="AI3">
-        <v>0.6329018032276829</v>
+        <v>0.6327739885777682</v>
       </c>
       <c r="AJ3">
-        <v>0.4454884331327572</v>
+        <v>0.4573297232673441</v>
       </c>
       <c r="AK3">
-        <v>0.5404091725095689</v>
+        <v>0.5725647873682975</v>
       </c>
       <c r="AL3">
-        <v>258.4</v>
+        <v>373.6</v>
       </c>
       <c r="AM3">
-        <v>258.4</v>
+        <v>373.6</v>
       </c>
       <c r="AN3">
-        <v>0.5117250732817081</v>
+        <v>0.7040497131394746</v>
       </c>
       <c r="AO3">
-        <v>35.23297213622292</v>
+        <v>19.00936830835117</v>
       </c>
       <c r="AP3">
-        <v>0.34900686879293</v>
+        <v>0.5473214661448471</v>
       </c>
       <c r="AQ3">
-        <v>35.23297213622292</v>
+        <v>19.00936830835117</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_insurance_life.xlsx
@@ -648,10 +648,10 @@
         <v>0.1790544275343627</v>
       </c>
       <c r="X2">
-        <v>0.1080474665909721</v>
+        <v>0.1080074470044095</v>
       </c>
       <c r="Y2">
-        <v>0.07100696094339054</v>
+        <v>0.07104698052995323</v>
       </c>
       <c r="Z2">
         <v>1.424397927039935</v>
@@ -660,10 +660,10 @@
         <v>1.069793042712461</v>
       </c>
       <c r="AB2">
-        <v>0.07472786949627339</v>
+        <v>0.07470866681373359</v>
       </c>
       <c r="AC2">
-        <v>0.9950651732161879</v>
+        <v>0.9950843758987278</v>
       </c>
       <c r="AD2">
         <v>5019.1</v>
@@ -785,10 +785,10 @@
         <v>0.1790544275343627</v>
       </c>
       <c r="X3">
-        <v>0.1080474665909721</v>
+        <v>0.1080074470044095</v>
       </c>
       <c r="Y3">
-        <v>0.07100696094339054</v>
+        <v>0.07104698052995323</v>
       </c>
       <c r="Z3">
         <v>1.424397927039935</v>
@@ -797,10 +797,10 @@
         <v>1.069793042712461</v>
       </c>
       <c r="AB3">
-        <v>0.07472786949627339</v>
+        <v>0.07470866681373359</v>
       </c>
       <c r="AC3">
-        <v>0.9950651732161879</v>
+        <v>0.9950843758987278</v>
       </c>
       <c r="AD3">
         <v>5019.1</v>
